--- a/sources/松下新风功能对比表.xlsx
+++ b/sources/松下新风功能对比表.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Panasonic\20260519 html_page\sources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waipc\Documents\GitHub\songxiaxinfeng\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A069FD-5FDA-4A16-A4FF-B33AA2BB656A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAD82A4-DA62-454A-A90F-9337ECDF82E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="214" yWindow="154" windowWidth="19183" windowHeight="11263" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="新风" sheetId="1" r:id="rId1"/>
+    <sheet name="除湿" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="86">
   <si>
     <t>产品系列</t>
   </si>
@@ -214,6 +215,101 @@
   </si>
   <si>
     <t>设备尺寸（高）</t>
+  </si>
+  <si>
+    <t>50NXC2C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZXC2C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZXH1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50NC1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>直流马达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国联保，整机3年，马达8年</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新风分类</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双向流全热交换</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单向流送风</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>排水泵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>滤网配置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FV-25ZXH1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FV-35ZXH1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50-150</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>除湿量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50-100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FV-25ZXC2C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FV-35ZXC2C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FV-50NXC2C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FV-50NC1C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">备注：
+1. 除湿全热类设备的除湿量测试工况为：室内27℃，50%相对湿度，室外35℃，60%相对湿度。
+2. 除湿新风类设备的除湿量测试工况为：室内30℃，80%相对湿度。
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>●</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -249,7 +345,7 @@
       <patternFill patternType="none"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -305,13 +401,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -333,6 +440,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -341,6 +460,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -608,230 +733,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="6" t="s">
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="6" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="G2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+      <c r="C3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="7"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+      <c r="C4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="7"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="C5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="7"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="C6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="7"/>
+      <c r="A7" s="11"/>
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="C7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:26" ht="18" customHeight="1">
-      <c r="A8" s="7"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="C8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:26" ht="18" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6" t="s">
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
     </row>
     <row r="10" spans="1:26" ht="18" customHeight="1">
-      <c r="A10" s="7"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
+      <c r="C10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -848,26 +973,26 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="18" customHeight="1">
-      <c r="A11" s="7"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="C11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -884,315 +1009,315 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="6"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="C12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:26" ht="18" customHeight="1">
-      <c r="A13" s="6"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="C13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" spans="1:26" ht="18" customHeight="1">
-      <c r="A14" s="6"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="C14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18" customHeight="1">
-      <c r="A15" s="6"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
+      <c r="C15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
     </row>
     <row r="16" spans="1:26" ht="18" customHeight="1">
-      <c r="A16" s="7"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
+      <c r="C16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
     </row>
     <row r="17" spans="1:26" ht="18" customHeight="1">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="C17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
     </row>
     <row r="18" spans="1:26" ht="18" customHeight="1">
-      <c r="A18" s="7"/>
+      <c r="A18" s="11"/>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="C18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
     </row>
     <row r="19" spans="1:26" ht="18" customHeight="1">
-      <c r="A19" s="7"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
+      <c r="C19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" spans="1:26" ht="18" customHeight="1">
-      <c r="A20" s="7"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="C20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
     </row>
     <row r="21" spans="1:26" ht="16.3">
-      <c r="A21" s="7"/>
+      <c r="A21" s="11"/>
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="C21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
     </row>
     <row r="22" spans="1:26" ht="16.3">
-      <c r="A22" s="7"/>
+      <c r="A22" s="11"/>
       <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="C22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
     </row>
     <row r="23" spans="1:26" ht="16.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="C23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
     </row>
     <row r="24" spans="1:26" ht="16.3">
-      <c r="A24" s="7"/>
+      <c r="A24" s="11"/>
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="C24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
     </row>
     <row r="25" spans="1:26" ht="16.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="6" t="s">
+      <c r="B25" s="13"/>
+      <c r="C25" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
     </row>
     <row r="26" spans="1:26" ht="16.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1230,7 +1355,7 @@
       </c>
     </row>
     <row r="27" spans="1:26" ht="16.3">
-      <c r="A27" s="6"/>
+      <c r="A27" s="10"/>
       <c r="B27" s="1" t="s">
         <v>48</v>
       </c>
@@ -1266,7 +1391,7 @@
       </c>
     </row>
     <row r="28" spans="1:26" ht="16.3">
-      <c r="A28" s="7"/>
+      <c r="A28" s="11"/>
       <c r="B28" s="1" t="s">
         <v>53</v>
       </c>
@@ -1302,7 +1427,7 @@
       </c>
     </row>
     <row r="29" spans="1:26" ht="16.3">
-      <c r="A29" s="7"/>
+      <c r="A29" s="11"/>
       <c r="B29" s="1" t="s">
         <v>54</v>
       </c>
@@ -1338,7 +1463,7 @@
       </c>
     </row>
     <row r="30" spans="1:26" ht="16.3">
-      <c r="A30" s="7"/>
+      <c r="A30" s="11"/>
       <c r="B30" s="1" t="s">
         <v>55</v>
       </c>
@@ -1374,7 +1499,7 @@
       </c>
     </row>
     <row r="31" spans="1:26" s="5" customFormat="1" ht="16.3">
-      <c r="A31" s="7"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="1" t="s">
         <v>56</v>
       </c>
@@ -1424,7 +1549,7 @@
       <c r="Z31" s="2"/>
     </row>
     <row r="32" spans="1:26" ht="16.3">
-      <c r="A32" s="7"/>
+      <c r="A32" s="11"/>
       <c r="B32" s="1" t="s">
         <v>57</v>
       </c>
@@ -1460,7 +1585,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="16.3">
-      <c r="A33" s="7"/>
+      <c r="A33" s="11"/>
       <c r="B33" s="1" t="s">
         <v>58</v>
       </c>
@@ -1496,7 +1621,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="16.3">
-      <c r="A34" s="7"/>
+      <c r="A34" s="11"/>
       <c r="B34" s="1" t="s">
         <v>59</v>
       </c>
@@ -1532,7 +1657,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="16.3">
-      <c r="A35" s="7"/>
+      <c r="A35" s="11"/>
       <c r="B35" s="1" t="s">
         <v>60</v>
       </c>
@@ -1568,7 +1693,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="16.3">
-      <c r="A36" s="7"/>
+      <c r="A36" s="11"/>
       <c r="B36" s="1" t="s">
         <v>61</v>
       </c>
@@ -1604,7 +1729,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="16.3">
-      <c r="A37" s="7"/>
+      <c r="A37" s="11"/>
       <c r="B37" s="1" t="s">
         <v>62</v>
       </c>
@@ -1725,5 +1850,963 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1BC2AB-D09B-4CE9-9A16-B51310423CDA}">
+  <dimension ref="A1:O45"/>
+  <sheetFormatPr defaultColWidth="13.86328125" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.86328125" style="5"/>
+    <col min="2" max="2" width="19" style="5" customWidth="1"/>
+    <col min="3" max="6" width="13.86328125" style="5"/>
+    <col min="7" max="7" width="14.73046875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.59765625" style="5" customWidth="1"/>
+    <col min="9" max="15" width="13.86328125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="18" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="14"/>
+      <c r="G1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" ht="18" customHeight="1">
+      <c r="A3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="14"/>
+      <c r="G3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="18" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="18" customHeight="1">
+      <c r="A5" s="10"/>
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="14"/>
+      <c r="G5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="18" customHeight="1">
+      <c r="A6" s="10"/>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="18" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A8" s="10"/>
+      <c r="B8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" ht="18" customHeight="1">
+      <c r="A9" s="11"/>
+      <c r="B9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" ht="18" customHeight="1">
+      <c r="A10" s="11"/>
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" ht="18" customHeight="1">
+      <c r="A11" s="10"/>
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="18" customHeight="1">
+      <c r="A12" s="10"/>
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="18" customHeight="1">
+      <c r="A13" s="10"/>
+      <c r="B13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="14"/>
+      <c r="G13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="18" customHeight="1">
+      <c r="A14" s="10"/>
+      <c r="B14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="18" customHeight="1">
+      <c r="A15" s="11"/>
+      <c r="B15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="18" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="18" customHeight="1">
+      <c r="A17" s="11"/>
+      <c r="B17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="18" customHeight="1">
+      <c r="A18" s="11"/>
+      <c r="B18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="18" customHeight="1">
+      <c r="A19" s="11"/>
+      <c r="B19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="14"/>
+      <c r="G19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="16.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="16.3">
+      <c r="A22" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="16.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="14"/>
+      <c r="E23" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16.3">
+      <c r="A24" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" spans="1:15" ht="16.3">
+      <c r="A25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="16.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="6">
+        <v>250</v>
+      </c>
+      <c r="D27" s="6">
+        <v>350</v>
+      </c>
+      <c r="E27" s="6">
+        <v>300</v>
+      </c>
+      <c r="F27" s="6">
+        <v>400</v>
+      </c>
+      <c r="G27" s="6">
+        <v>500</v>
+      </c>
+      <c r="H27" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="7" customFormat="1" ht="16.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="6">
+        <v>81</v>
+      </c>
+      <c r="D28" s="6">
+        <v>110</v>
+      </c>
+      <c r="E28" s="6">
+        <v>65</v>
+      </c>
+      <c r="F28" s="6">
+        <v>77</v>
+      </c>
+      <c r="G28" s="6">
+        <v>45</v>
+      </c>
+      <c r="H28" s="6">
+        <v>45</v>
+      </c>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15" ht="16.3">
+      <c r="A29" s="11"/>
+      <c r="B29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="6">
+        <v>110</v>
+      </c>
+      <c r="D29" s="6">
+        <v>110</v>
+      </c>
+      <c r="E29" s="6">
+        <v>120</v>
+      </c>
+      <c r="F29" s="6">
+        <v>120</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="16.3">
+      <c r="A30" s="11"/>
+      <c r="B30" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1110</v>
+      </c>
+      <c r="D30" s="6">
+        <v>1490</v>
+      </c>
+      <c r="E30" s="6">
+        <v>815</v>
+      </c>
+      <c r="F30" s="6">
+        <v>895</v>
+      </c>
+      <c r="G30" s="6">
+        <v>635</v>
+      </c>
+      <c r="H30" s="6">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" s="5" customFormat="1" ht="16.3">
+      <c r="A31" s="11"/>
+      <c r="B31" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" ht="16.3">
+      <c r="A32" s="11"/>
+      <c r="B32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.78</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.72</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0.72</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="16.3">
+      <c r="A33" s="11"/>
+      <c r="B33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="6">
+        <v>32</v>
+      </c>
+      <c r="D33" s="6">
+        <v>38</v>
+      </c>
+      <c r="E33" s="6">
+        <v>40</v>
+      </c>
+      <c r="F33" s="6">
+        <v>41</v>
+      </c>
+      <c r="G33" s="6">
+        <v>39</v>
+      </c>
+      <c r="H33" s="6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="16.3">
+      <c r="A34" s="11"/>
+      <c r="B34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="4">
+        <v>95</v>
+      </c>
+      <c r="D34" s="4">
+        <v>95</v>
+      </c>
+      <c r="E34" s="4">
+        <v>68</v>
+      </c>
+      <c r="F34" s="4">
+        <v>78</v>
+      </c>
+      <c r="G34" s="4">
+        <v>45</v>
+      </c>
+      <c r="H34" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="16.3">
+      <c r="A35" s="11"/>
+      <c r="B35" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1297</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1297</v>
+      </c>
+      <c r="E35" s="4">
+        <v>1330</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1330</v>
+      </c>
+      <c r="G35" s="4">
+        <v>950</v>
+      </c>
+      <c r="H35" s="4">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="16.3">
+      <c r="A36" s="11"/>
+      <c r="B36" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="4">
+        <v>997</v>
+      </c>
+      <c r="D36" s="4">
+        <v>997</v>
+      </c>
+      <c r="E36" s="4">
+        <v>760</v>
+      </c>
+      <c r="F36" s="4">
+        <v>799</v>
+      </c>
+      <c r="G36" s="4">
+        <v>570</v>
+      </c>
+      <c r="H36" s="4">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="16.3">
+      <c r="A37" s="11"/>
+      <c r="B37" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="4">
+        <v>250</v>
+      </c>
+      <c r="D37" s="4">
+        <v>250</v>
+      </c>
+      <c r="E37" s="4">
+        <v>280</v>
+      </c>
+      <c r="F37" s="4">
+        <v>280</v>
+      </c>
+      <c r="G37" s="4">
+        <v>288</v>
+      </c>
+      <c r="H37" s="4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="18" customHeight="1">
+      <c r="A38" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="18" customHeight="1">
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+    </row>
+    <row r="41" spans="1:15" ht="18" customHeight="1">
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+    </row>
+    <row r="42" spans="1:15" ht="18" customHeight="1">
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+    </row>
+    <row r="43" spans="1:15" ht="18" customHeight="1">
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+    </row>
+    <row r="44" spans="1:15" ht="18" customHeight="1">
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+    </row>
+    <row r="45" spans="1:15" ht="18" customHeight="1">
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:A37"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E4:F4"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>